--- a/Resultados5_ListaResultados_21022026.xlsx
+++ b/Resultados5_ListaResultados_21022026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uredu.sharepoint.com/sites/ControlTabacoFacultadEconomica/Documentos compartidos/DCE e-cig/Resultados finales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1141" documentId="8_{1059A956-481A-4C4A-9BFB-C7336247E0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{733909F0-C81E-49DB-8FA1-FF29186FE1D5}"/>
+  <xr:revisionPtr revIDLastSave="1257" documentId="8_{1059A956-481A-4C4A-9BFB-C7336247E0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA25AFA2-B099-475F-9741-735BC0539FC1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1290" yWindow="3270" windowWidth="15375" windowHeight="7785" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indice Tablas" sheetId="7" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Tabla 3" sheetId="10" r:id="rId4"/>
     <sheet name="Tabla 4" sheetId="13" r:id="rId5"/>
     <sheet name="Tabla 5" sheetId="15" r:id="rId6"/>
+    <sheet name="Tabla B8" sheetId="18" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -227,7 +226,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="285">
   <si>
     <t xml:space="preserve">Tabla 1 </t>
   </si>
@@ -1020,6 +1019,69 @@
   <si>
     <t>Vapeadores exclusivos</t>
   </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>bflavour1_mu</t>
+  </si>
+  <si>
+    <t>bflavour1_sig</t>
+  </si>
+  <si>
+    <t>bflavour2_mu</t>
+  </si>
+  <si>
+    <t>bflavour2_sig</t>
+  </si>
+  <si>
+    <t>RLH overall</t>
+  </si>
+  <si>
+    <t>RLH random benchmark</t>
+  </si>
+  <si>
+    <t>RLH p5</t>
+  </si>
+  <si>
+    <t>RLH p25</t>
+  </si>
+  <si>
+    <t>RLH median</t>
+  </si>
+  <si>
+    <t>RLH p75</t>
+  </si>
+  <si>
+    <t>RLH p95</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>180 or more</t>
+  </si>
+  <si>
+    <t>90 or more</t>
+  </si>
+  <si>
+    <t>60 or more</t>
+  </si>
+  <si>
+    <t>150 or more</t>
+  </si>
+  <si>
+    <t>120 or more</t>
+  </si>
+  <si>
+    <t>210 or more</t>
+  </si>
+  <si>
+    <t>240 or more</t>
+  </si>
+  <si>
+    <t>270 or more</t>
+  </si>
 </sst>
 </file>
 
@@ -1029,9 +1091,9 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.000000000000"/>
+    <numFmt numFmtId="167" formatCode="0.000000000000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1150,8 +1212,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1209,6 +1285,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1309,7 +1391,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1363,21 +1445,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1397,10 +1479,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1690,340 +1768,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
+      <c r="A1" s="51"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
-      <c r="B3" s="56" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
-      <c r="B5" s="56" t="s">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="55" t="s">
+      <c r="A6" s="51"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55" t="s">
+      <c r="D6" s="51"/>
+      <c r="E6" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55" t="s">
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55" t="s">
+      <c r="I6" s="51"/>
+      <c r="J6" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="55"/>
+      <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55" t="s">
+      <c r="D9" s="51"/>
+      <c r="E9" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55" t="s">
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55" t="s">
+      <c r="I9" s="51"/>
+      <c r="J9" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="55"/>
+      <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="56" t="s">
+      <c r="A10" s="51"/>
+      <c r="B10" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55" t="s">
+      <c r="D12" s="51"/>
+      <c r="E12" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55" t="s">
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55" t="s">
+      <c r="I12" s="51"/>
+      <c r="J12" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="55"/>
+      <c r="K12" s="51"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
-      <c r="B13" s="56" t="s">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="55"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55" t="s">
+      <c r="D15" s="51"/>
+      <c r="E15" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="55"/>
+      <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="55"/>
-      <c r="B16" s="56" t="s">
+      <c r="A16" s="51"/>
+      <c r="B16" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="55"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="55"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="55"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
@@ -2037,7 +2115,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189302D9-159C-4686-95B8-8B76A6877983}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.85546875" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
@@ -3279,7 +3357,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>69</v>
       </c>
@@ -3311,7 +3389,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>70</v>
       </c>
@@ -3346,7 +3424,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>72</v>
       </c>
@@ -3381,7 +3459,6 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:36" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:36" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>74</v>
@@ -6180,16 +6257,16 @@
       <c r="AA70" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="AB70" s="46" t="s">
+      <c r="AB70" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="AC70" s="46" t="s">
+      <c r="AC70" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="AD70" s="46" t="s">
+      <c r="AD70" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="AE70" s="46" t="s">
+      <c r="AE70" s="45" t="s">
         <v>233</v>
       </c>
       <c r="AF70" s="40" t="s">
@@ -6528,7 +6605,7 @@
         <f t="shared" ref="K4:K29" si="0">IF(ABS(J4)&gt;2.576,"***",IF(ABS(J4)&gt;1.96,"**",IF(ABS(J4)&gt;1.645,"*","")))</f>
         <v/>
       </c>
-      <c r="L4" s="53" t="s">
+      <c r="L4" s="49" t="s">
         <v>258</v>
       </c>
       <c r="O4" s="2" t="str">
@@ -9336,7 +9413,7 @@
         <f t="shared" ref="K59:K64" si="31">IF(ABS(J59)&gt;2.576,"***",IF(ABS(J59)&gt;1.96,"**",IF(ABS(J59)&gt;1.645,"*","")))</f>
         <v>***</v>
       </c>
-      <c r="L59" s="54" t="s">
+      <c r="L59" s="50" t="s">
         <v>258</v>
       </c>
       <c r="M59" s="32"/>
@@ -11957,7 +12034,7 @@
       <c r="AA103" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="AB103" s="52" t="s">
+      <c r="AB103" s="48" t="s">
         <v>225</v>
       </c>
       <c r="AC103" s="27" t="s">
@@ -12117,7 +12194,7 @@
     </row>
     <row r="107" spans="4:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F107" s="6"/>
-      <c r="G107" s="44" t="s">
+      <c r="G107" s="36" t="s">
         <v>132</v>
       </c>
     </row>
@@ -13263,7 +13340,7 @@
         <f t="shared" si="48"/>
         <v>12.7615098265305, 143.202580300568, 68.0635400546204, 36.3296767896028, 91.2238512240861, 75.3716483435896, 72.7309299819046, 32.8780713083573, 19.1556954293508, 13.2516492803317</v>
       </c>
-      <c r="AB120" s="52" t="s">
+      <c r="AB120" s="48" t="s">
         <v>250</v>
       </c>
       <c r="AC120" s="27" t="s">
@@ -13423,7 +13500,7 @@
       <c r="F124" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G124" s="44" t="s">
+      <c r="G124" s="36" t="s">
         <v>134</v>
       </c>
       <c r="AB124" s="14"/>
@@ -14568,7 +14645,7 @@
       <c r="AA137" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="AB137" s="52" t="s">
+      <c r="AB137" s="48" t="s">
         <v>228</v>
       </c>
       <c r="AC137" s="27" t="s">
@@ -14919,14 +14996,14 @@
         <f t="shared" ref="K4:K9" si="0">IF(ABS(J5)&gt;2.576,"***",IF(ABS(J5)&gt;1.96,"**",IF(ABS(J5)&gt;1.645,"*","")))</f>
         <v>***</v>
       </c>
-      <c r="L4" s="51" t="s">
+      <c r="L4" s="47" t="s">
         <v>257</v>
       </c>
       <c r="O4" s="2" t="str">
         <f>IF(ABS(N4)&gt;2.576,"***",IF(ABS(N4)&gt;1.96,"**",IF(ABS(N4)&gt;1.645,"*","")))</f>
         <v/>
       </c>
-      <c r="P4" s="48">
+      <c r="P4" s="30">
         <v>-12.501255797344228</v>
       </c>
       <c r="Q4" s="30">
@@ -14939,7 +15016,6 @@
         <f t="shared" ref="S4:S9" si="1">IF(ABS(R4)&gt;2.576,"***",IF(ABS(R4)&gt;1.96,"**",IF(ABS(R4)&gt;1.645,"*","")))</f>
         <v>***</v>
       </c>
-      <c r="T4" s="49"/>
       <c r="W4" s="2" t="str">
         <f t="shared" ref="W4:W9" si="2">IF(ABS(V4)&gt;2.576,"***",IF(ABS(V4)&gt;1.96,"**",IF(ABS(V4)&gt;1.645,"*","")))</f>
         <v/>
@@ -16297,7 +16373,7 @@
         <f t="shared" ref="K35:K40" si="5">IF(ABS(J35)&gt;2.576,"***",IF(ABS(J35)&gt;1.96,"**",IF(ABS(J35)&gt;1.645,"*","")))</f>
         <v/>
       </c>
-      <c r="L35" s="51" t="s">
+      <c r="L35" s="47" t="s">
         <v>257</v>
       </c>
       <c r="O35" s="2" t="str">
@@ -19558,13 +19634,13 @@
       <c r="W97" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="X97" s="45" t="s">
+      <c r="X97" s="44" t="s">
         <v>243</v>
       </c>
-      <c r="Y97" s="45" t="s">
+      <c r="Y97" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="Z97" s="45" t="s">
+      <c r="Z97" s="44" t="s">
         <v>244</v>
       </c>
       <c r="AA97" s="40" t="s">
@@ -19705,7 +19781,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19786,7 +19862,7 @@
       <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="30">
         <v>-1.6362193388148158</v>
       </c>
       <c r="E4" s="30">
@@ -19799,7 +19875,7 @@
         <f t="shared" ref="G4:G9" si="0">IF(ABS(F5)&gt;2.576,"***",IF(ABS(F5)&gt;1.96,"**",IF(ABS(F5)&gt;1.645,"*","")))</f>
         <v>***</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="35">
         <v>-5.7211243714078739</v>
       </c>
       <c r="I4" s="35">
@@ -19825,7 +19901,7 @@
         <f t="shared" ref="O4:O9" si="1">IF(ABS(N4)&gt;2.576,"***",IF(ABS(N4)&gt;1.96,"**",IF(ABS(N4)&gt;1.645,"*","")))</f>
         <v>***</v>
       </c>
-      <c r="P4" s="49">
+      <c r="P4">
         <v>-23.682762509270677</v>
       </c>
       <c r="Q4">
@@ -21309,7 +21385,7 @@
         <f t="shared" ref="G35:G40" si="4">IF(ABS(F35)&gt;2.576,"***",IF(ABS(F35)&gt;1.96,"**",IF(ABS(F35)&gt;1.645,"*","")))</f>
         <v/>
       </c>
-      <c r="H35" s="50">
+      <c r="H35" s="35">
         <v>-9.0160377201644888</v>
       </c>
       <c r="I35" s="35">
@@ -21322,7 +21398,7 @@
         <f t="shared" ref="K35:K40" si="5">IF(ABS(J35)&gt;2.576,"***",IF(ABS(J35)&gt;1.96,"**",IF(ABS(J35)&gt;1.645,"*","")))</f>
         <v/>
       </c>
-      <c r="L35" s="48">
+      <c r="L35" s="30">
         <v>-15.597852315706572</v>
       </c>
       <c r="M35" s="30">
@@ -21335,7 +21411,7 @@
         <f t="shared" ref="O35:O40" si="6">IF(ABS(N35)&gt;2.576,"***",IF(ABS(N35)&gt;1.96,"**",IF(ABS(N35)&gt;1.645,"*","")))</f>
         <v>***</v>
       </c>
-      <c r="P35" s="48">
+      <c r="P35" s="30">
         <v>-6.0428928798927783</v>
       </c>
       <c r="Q35" s="30">
@@ -23920,16 +23996,16 @@
       <c r="U78" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="V78" s="46" t="s">
+      <c r="V78" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="W78" s="46" t="s">
+      <c r="W78" s="45" t="s">
         <v>235</v>
       </c>
-      <c r="X78" s="46" t="s">
+      <c r="X78" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="Y78" s="46" t="s">
+      <c r="Y78" s="45" t="s">
         <v>236</v>
       </c>
       <c r="Z78" s="29" t="s">
@@ -25186,16 +25262,16 @@
       <c r="U97" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="V97" s="46" t="s">
+      <c r="V97" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="W97" s="46" t="s">
+      <c r="W97" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="X97" s="46" t="s">
+      <c r="X97" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="Y97" s="47" t="s">
+      <c r="Y97" s="46" t="s">
         <v>240</v>
       </c>
       <c r="Z97" s="40" t="s">
@@ -25353,7 +25429,3813 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4B425E-5558-4D6C-87D6-CD25FC0A4AB8}">
+  <dimension ref="A1:AC63"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K1" t="s">
+        <v>278</v>
+      </c>
+      <c r="L1" t="s">
+        <v>281</v>
+      </c>
+      <c r="M1" t="s">
+        <v>281</v>
+      </c>
+      <c r="N1" t="s">
+        <v>281</v>
+      </c>
+      <c r="O1" t="s">
+        <v>280</v>
+      </c>
+      <c r="P1" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>280</v>
+      </c>
+      <c r="R1" t="s">
+        <v>277</v>
+      </c>
+      <c r="S1" t="s">
+        <v>277</v>
+      </c>
+      <c r="T1" t="s">
+        <v>277</v>
+      </c>
+      <c r="U1" t="s">
+        <v>282</v>
+      </c>
+      <c r="V1" t="s">
+        <v>282</v>
+      </c>
+      <c r="W1" t="s">
+        <v>282</v>
+      </c>
+      <c r="X1" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>283</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B2" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="W2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="X2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC2" s="54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>1.4867725652737109</v>
+      </c>
+      <c r="D3">
+        <v>8.9737638997784058E-2</v>
+      </c>
+      <c r="E3">
+        <v>16.567992894379859</v>
+      </c>
+      <c r="F3">
+        <v>1.5104</v>
+      </c>
+      <c r="G3">
+        <v>9.2552871036038306E-2</v>
+      </c>
+      <c r="H3">
+        <v>18.369115824921209</v>
+      </c>
+      <c r="I3">
+        <v>1.586976711355665</v>
+      </c>
+      <c r="J3">
+        <v>9.3645742881582741E-2</v>
+      </c>
+      <c r="K3">
+        <v>16.946597490955181</v>
+      </c>
+      <c r="L3">
+        <v>1.700114407989983</v>
+      </c>
+      <c r="M3">
+        <v>9.2552871036038306E-2</v>
+      </c>
+      <c r="N3">
+        <v>18.369115824921209</v>
+      </c>
+      <c r="O3">
+        <v>1.9443953978896971</v>
+      </c>
+      <c r="P3">
+        <v>0.1058783700349844</v>
+      </c>
+      <c r="Q3">
+        <v>18.36442511579304</v>
+      </c>
+      <c r="R3">
+        <v>1.9808617574844389</v>
+      </c>
+      <c r="S3">
+        <v>0.1147435851274801</v>
+      </c>
+      <c r="T3">
+        <v>17.263376904980809</v>
+      </c>
+      <c r="U3">
+        <v>2.3732668072132079</v>
+      </c>
+      <c r="V3">
+        <v>0.13317409040969669</v>
+      </c>
+      <c r="W3">
+        <v>17.820784808156692</v>
+      </c>
+      <c r="X3">
+        <v>2.425558270436301</v>
+      </c>
+      <c r="Y3">
+        <v>0.1453188196680818</v>
+      </c>
+      <c r="Z3">
+        <v>16.69128799680897</v>
+      </c>
+      <c r="AA3">
+        <v>2.532306923440919</v>
+      </c>
+      <c r="AB3">
+        <v>0.16045189532498161</v>
+      </c>
+      <c r="AC3">
+        <v>15.78234347629205</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>2.118504563988147</v>
+      </c>
+      <c r="D4">
+        <v>0.1017475062886377</v>
+      </c>
+      <c r="E4">
+        <v>20.821193965956919</v>
+      </c>
+      <c r="F4">
+        <v>2.0853000000000002</v>
+      </c>
+      <c r="G4">
+        <v>0.1020088486756888</v>
+      </c>
+      <c r="H4">
+        <v>20.009024238756091</v>
+      </c>
+      <c r="I4">
+        <v>2.1355408597739141</v>
+      </c>
+      <c r="J4">
+        <v>0.1051252558368487</v>
+      </c>
+      <c r="K4">
+        <v>20.314251249844379</v>
+      </c>
+      <c r="L4">
+        <v>2.0410975257194601</v>
+      </c>
+      <c r="M4">
+        <v>0.1020088486756888</v>
+      </c>
+      <c r="N4">
+        <v>20.009024238756091</v>
+      </c>
+      <c r="O4">
+        <v>1.964707841494556</v>
+      </c>
+      <c r="P4">
+        <v>0.1099215870462449</v>
+      </c>
+      <c r="Q4">
+        <v>17.873721570886602</v>
+      </c>
+      <c r="R4">
+        <v>2.013329478315411</v>
+      </c>
+      <c r="S4">
+        <v>0.1192180683926789</v>
+      </c>
+      <c r="T4">
+        <v>16.88778811349243</v>
+      </c>
+      <c r="U4">
+        <v>1.9368060495710631</v>
+      </c>
+      <c r="V4">
+        <v>0.13035114538912859</v>
+      </c>
+      <c r="W4">
+        <v>14.85837384695964</v>
+      </c>
+      <c r="X4">
+        <v>1.9608967227181411</v>
+      </c>
+      <c r="Y4">
+        <v>0.14862817704133491</v>
+      </c>
+      <c r="Z4">
+        <v>13.19330400030942</v>
+      </c>
+      <c r="AA4">
+        <v>1.883770589693224</v>
+      </c>
+      <c r="AB4">
+        <v>0.14939503779106239</v>
+      </c>
+      <c r="AC4">
+        <v>12.60932503211912</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>2.1009291744346692</v>
+      </c>
+      <c r="D5">
+        <v>0.1023433371278087</v>
+      </c>
+      <c r="E5">
+        <v>20.528245740228119</v>
+      </c>
+      <c r="F5">
+        <v>2.1006999999999998</v>
+      </c>
+      <c r="G5">
+        <v>0.1057391514066104</v>
+      </c>
+      <c r="H5">
+        <v>20.553084127762141</v>
+      </c>
+      <c r="I5">
+        <v>2.1722368248826132</v>
+      </c>
+      <c r="J5">
+        <v>0.1056335072870658</v>
+      </c>
+      <c r="K5">
+        <v>20.563899473482589</v>
+      </c>
+      <c r="L5">
+        <v>2.173265674458241</v>
+      </c>
+      <c r="M5">
+        <v>0.1057391514066104</v>
+      </c>
+      <c r="N5">
+        <v>20.553084127762141</v>
+      </c>
+      <c r="O5">
+        <v>2.4899948750882048</v>
+      </c>
+      <c r="P5">
+        <v>0.1214388006936314</v>
+      </c>
+      <c r="Q5">
+        <v>20.504112860682969</v>
+      </c>
+      <c r="R5">
+        <v>2.6807308495631341</v>
+      </c>
+      <c r="S5">
+        <v>0.1301941572597454</v>
+      </c>
+      <c r="T5">
+        <v>20.590254631894961</v>
+      </c>
+      <c r="U5">
+        <v>2.8734070719567208</v>
+      </c>
+      <c r="V5">
+        <v>0.14690164714697859</v>
+      </c>
+      <c r="W5">
+        <v>19.560073884548139</v>
+      </c>
+      <c r="X5">
+        <v>2.943722185557117</v>
+      </c>
+      <c r="Y5">
+        <v>0.1655907879143981</v>
+      </c>
+      <c r="Z5">
+        <v>17.777089067773922</v>
+      </c>
+      <c r="AA5">
+        <v>2.987794752004036</v>
+      </c>
+      <c r="AB5">
+        <v>0.17378639821128469</v>
+      </c>
+      <c r="AC5">
+        <v>17.19233946244491</v>
+      </c>
+    </row>
+    <row r="6" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>-2.7904721949240159</v>
+      </c>
+      <c r="D6">
+        <v>0.1166940650315508</v>
+      </c>
+      <c r="E6">
+        <v>-23.912717362014519</v>
+      </c>
+      <c r="F6">
+        <v>-2.7677999999999998</v>
+      </c>
+      <c r="G6">
+        <v>0.1181232045818212</v>
+      </c>
+      <c r="H6">
+        <v>-23.556629490404781</v>
+      </c>
+      <c r="I6">
+        <v>-2.811892035836324</v>
+      </c>
+      <c r="J6">
+        <v>0.1212886357609981</v>
+      </c>
+      <c r="K6">
+        <v>-23.1834748424182</v>
+      </c>
+      <c r="L6">
+        <v>-2.7825845645532459</v>
+      </c>
+      <c r="M6">
+        <v>0.1181232045818212</v>
+      </c>
+      <c r="N6">
+        <v>-23.556629490404781</v>
+      </c>
+      <c r="O6">
+        <v>-2.6381856996664581</v>
+      </c>
+      <c r="P6">
+        <v>0.1281635084783242</v>
+      </c>
+      <c r="Q6">
+        <v>-20.584530893305281</v>
+      </c>
+      <c r="R6">
+        <v>-2.4804431528757989</v>
+      </c>
+      <c r="S6">
+        <v>0.12615877241817319</v>
+      </c>
+      <c r="T6">
+        <v>-19.661281616263491</v>
+      </c>
+      <c r="U6">
+        <v>-2.5357513273554702</v>
+      </c>
+      <c r="V6">
+        <v>0.1396971081790781</v>
+      </c>
+      <c r="W6">
+        <v>-18.151781095603521</v>
+      </c>
+      <c r="X6">
+        <v>-2.5098302408261199</v>
+      </c>
+      <c r="Y6">
+        <v>0.15572413516663999</v>
+      </c>
+      <c r="Z6">
+        <v>-16.11715639416046</v>
+      </c>
+      <c r="AA6">
+        <v>-2.3586170222731919</v>
+      </c>
+      <c r="AB6">
+        <v>0.15381602839411909</v>
+      </c>
+      <c r="AC6">
+        <v>-15.334013281306181</v>
+      </c>
+    </row>
+    <row r="7" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>5.3026584583495788</v>
+      </c>
+      <c r="D7">
+        <v>0.20212383535732931</v>
+      </c>
+      <c r="E7">
+        <v>26.23470136006053</v>
+      </c>
+      <c r="F7">
+        <v>5.2610999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0.2027378288450554</v>
+      </c>
+      <c r="H7">
+        <v>25.784856053444891</v>
+      </c>
+      <c r="I7">
+        <v>5.4521817553981116</v>
+      </c>
+      <c r="J7">
+        <v>0.2138639920282612</v>
+      </c>
+      <c r="K7">
+        <v>25.493687383697718</v>
+      </c>
+      <c r="L7">
+        <v>5.227565733357701</v>
+      </c>
+      <c r="M7">
+        <v>0.2027378288450554</v>
+      </c>
+      <c r="N7">
+        <v>25.784856053444891</v>
+      </c>
+      <c r="O7">
+        <v>5.7578250757526037</v>
+      </c>
+      <c r="P7">
+        <v>0.2475496741015861</v>
+      </c>
+      <c r="Q7">
+        <v>23.259271484194262</v>
+      </c>
+      <c r="R7">
+        <v>5.7706605852707016</v>
+      </c>
+      <c r="S7">
+        <v>0.25963122203220063</v>
+      </c>
+      <c r="T7">
+        <v>22.226373777784701</v>
+      </c>
+      <c r="U7">
+        <v>6.4284812749103653</v>
+      </c>
+      <c r="V7">
+        <v>0.30979268083333039</v>
+      </c>
+      <c r="W7">
+        <v>20.750913990666259</v>
+      </c>
+      <c r="X7">
+        <v>6.2838749837224164</v>
+      </c>
+      <c r="Y7">
+        <v>0.32805231530236412</v>
+      </c>
+      <c r="Z7">
+        <v>19.155100240431469</v>
+      </c>
+      <c r="AA7">
+        <v>6.374020616660486</v>
+      </c>
+      <c r="AB7">
+        <v>0.36003122219903222</v>
+      </c>
+      <c r="AC7">
+        <v>17.704077378980219</v>
+      </c>
+    </row>
+    <row r="8" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>-4.0830468421715231</v>
+      </c>
+      <c r="D8">
+        <v>0.16195018321255511</v>
+      </c>
+      <c r="E8">
+        <v>-25.211745742903151</v>
+      </c>
+      <c r="F8">
+        <v>-4.125</v>
+      </c>
+      <c r="G8">
+        <v>0.1613364427239723</v>
+      </c>
+      <c r="H8">
+        <v>-24.66352776088765</v>
+      </c>
+      <c r="I8">
+        <v>-4.2515315108291283</v>
+      </c>
+      <c r="J8">
+        <v>0.1721224534570214</v>
+      </c>
+      <c r="K8">
+        <v>-24.700621130123078</v>
+      </c>
+      <c r="L8">
+        <v>-3.979125833965552</v>
+      </c>
+      <c r="M8">
+        <v>0.1613364427239723</v>
+      </c>
+      <c r="N8">
+        <v>-24.66352776088765</v>
+      </c>
+      <c r="O8">
+        <v>-4.1230722704136076</v>
+      </c>
+      <c r="P8">
+        <v>0.18746898093703679</v>
+      </c>
+      <c r="Q8">
+        <v>-21.993357246649669</v>
+      </c>
+      <c r="R8">
+        <v>-4.0389419769378554</v>
+      </c>
+      <c r="S8">
+        <v>0.19403931347252079</v>
+      </c>
+      <c r="T8">
+        <v>-20.81507043421815</v>
+      </c>
+      <c r="U8">
+        <v>-4.231917276612398</v>
+      </c>
+      <c r="V8">
+        <v>0.23385718665171659</v>
+      </c>
+      <c r="W8">
+        <v>-18.096160897184621</v>
+      </c>
+      <c r="X8">
+        <v>-3.879648571885649</v>
+      </c>
+      <c r="Y8">
+        <v>0.23757572361244139</v>
+      </c>
+      <c r="Z8">
+        <v>-16.33015576210363</v>
+      </c>
+      <c r="AA8">
+        <v>-4.2593982336423712</v>
+      </c>
+      <c r="AB8">
+        <v>0.27466868611106687</v>
+      </c>
+      <c r="AC8">
+        <v>-15.507403825130661</v>
+      </c>
+    </row>
+    <row r="9" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="55">
+        <v>-5.9169213517622392</v>
+      </c>
+      <c r="D9">
+        <v>0.69026917236228602</v>
+      </c>
+      <c r="E9">
+        <v>-8.5719043942132735</v>
+      </c>
+      <c r="F9">
+        <v>-3.6960000000000002</v>
+      </c>
+      <c r="G9">
+        <v>0.35865653679157378</v>
+      </c>
+      <c r="H9">
+        <v>-6.4538781761360671</v>
+      </c>
+      <c r="I9">
+        <v>-3.5147010690598668</v>
+      </c>
+      <c r="J9">
+        <v>0.44139367347149161</v>
+      </c>
+      <c r="K9">
+        <v>-7.9627354905594769</v>
+      </c>
+      <c r="L9">
+        <v>-2.3147255955276811</v>
+      </c>
+      <c r="M9">
+        <v>0.35865653679157378</v>
+      </c>
+      <c r="N9">
+        <v>-6.4538781761360671</v>
+      </c>
+      <c r="O9">
+        <v>-1.6319391125820071</v>
+      </c>
+      <c r="P9">
+        <v>0.31251817853874159</v>
+      </c>
+      <c r="Q9">
+        <v>-5.2219013953445979</v>
+      </c>
+      <c r="R9">
+        <v>-1.083071627916653</v>
+      </c>
+      <c r="S9">
+        <v>0.29373731188972219</v>
+      </c>
+      <c r="T9">
+        <v>-3.687211614176106</v>
+      </c>
+      <c r="U9">
+        <v>-0.42111198385070941</v>
+      </c>
+      <c r="V9">
+        <v>0.25261454774060849</v>
+      </c>
+      <c r="W9">
+        <v>-1.6670139848126191</v>
+      </c>
+      <c r="X9">
+        <v>-0.34552389632603769</v>
+      </c>
+      <c r="Y9">
+        <v>0.2681512195308613</v>
+      </c>
+      <c r="Z9">
+        <v>-1.288541207944317</v>
+      </c>
+      <c r="AA9">
+        <v>-0.32273770967317572</v>
+      </c>
+      <c r="AB9">
+        <v>0.26805948295921228</v>
+      </c>
+      <c r="AC9">
+        <v>-1.2039779608255201</v>
+      </c>
+    </row>
+    <row r="10" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10">
+        <v>-6.3094125452290228</v>
+      </c>
+      <c r="D10">
+        <v>0.41971632602526598</v>
+      </c>
+      <c r="E10">
+        <v>-15.03256402956603</v>
+      </c>
+      <c r="F10">
+        <v>4.9440999999999997</v>
+      </c>
+      <c r="G10">
+        <v>0.1995248745638902</v>
+      </c>
+      <c r="H10">
+        <v>-18.7087667330273</v>
+      </c>
+      <c r="I10">
+        <v>-4.9636906643763048</v>
+      </c>
+      <c r="J10">
+        <v>0.2755855701044444</v>
+      </c>
+      <c r="K10">
+        <v>-18.011431667104741</v>
+      </c>
+      <c r="L10">
+        <v>-3.732864335652355</v>
+      </c>
+      <c r="M10">
+        <v>0.1995248745638902</v>
+      </c>
+      <c r="N10">
+        <v>-18.7087667330273</v>
+      </c>
+      <c r="O10">
+        <v>-3.4917913246451131</v>
+      </c>
+      <c r="P10">
+        <v>0.18036713350043251</v>
+      </c>
+      <c r="Q10">
+        <v>-19.35935476092012</v>
+      </c>
+      <c r="R10">
+        <v>3.140799459371642</v>
+      </c>
+      <c r="S10">
+        <v>0.1691438898986547</v>
+      </c>
+      <c r="T10">
+        <v>18.568802344876321</v>
+      </c>
+      <c r="U10">
+        <v>2.6471158388151759</v>
+      </c>
+      <c r="V10">
+        <v>0.1467736314019395</v>
+      </c>
+      <c r="W10">
+        <v>18.035363801594929</v>
+      </c>
+      <c r="X10">
+        <v>2.530796303621917</v>
+      </c>
+      <c r="Y10">
+        <v>0.14653118665053641</v>
+      </c>
+      <c r="Z10">
+        <v>17.271383392653721</v>
+      </c>
+      <c r="AA10">
+        <v>-2.4960493716370018</v>
+      </c>
+      <c r="AB10">
+        <v>0.1405812038768792</v>
+      </c>
+      <c r="AC10">
+        <v>-17.755214088385799</v>
+      </c>
+    </row>
+    <row r="11" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11">
+        <v>-0.36706142064956271</v>
+      </c>
+      <c r="D11">
+        <v>5.3438837805580078E-2</v>
+      </c>
+      <c r="E11">
+        <v>-6.8688136891187046</v>
+      </c>
+      <c r="F11">
+        <v>-0.35349999999999998</v>
+      </c>
+      <c r="G11">
+        <v>5.3742521755827742E-2</v>
+      </c>
+      <c r="H11">
+        <v>-7.1521469638251141</v>
+      </c>
+      <c r="I11">
+        <v>-0.38842738666081872</v>
+      </c>
+      <c r="J11">
+        <v>5.5204780696746357E-2</v>
+      </c>
+      <c r="K11">
+        <v>-7.0361186433208989</v>
+      </c>
+      <c r="L11">
+        <v>-0.38437441380424853</v>
+      </c>
+      <c r="M11">
+        <v>5.3742521755827742E-2</v>
+      </c>
+      <c r="N11">
+        <v>-7.1521469638251141</v>
+      </c>
+      <c r="O11">
+        <v>-0.45513501474384499</v>
+      </c>
+      <c r="P11">
+        <v>6.047682014081484E-2</v>
+      </c>
+      <c r="Q11">
+        <v>-7.5257762177988869</v>
+      </c>
+      <c r="R11">
+        <v>-0.45911209975605383</v>
+      </c>
+      <c r="S11">
+        <v>6.6782229016981845E-2</v>
+      </c>
+      <c r="T11">
+        <v>-6.8747645371242037</v>
+      </c>
+      <c r="U11">
+        <v>-0.51213280480948542</v>
+      </c>
+      <c r="V11">
+        <v>7.4248620033422405E-2</v>
+      </c>
+      <c r="W11">
+        <v>-6.8975397061784189</v>
+      </c>
+      <c r="X11">
+        <v>-0.54168843748115192</v>
+      </c>
+      <c r="Y11">
+        <v>8.3036336446448977E-2</v>
+      </c>
+      <c r="Z11">
+        <v>-6.5235107985585632</v>
+      </c>
+      <c r="AA11">
+        <v>-0.50757362048910626</v>
+      </c>
+      <c r="AB11">
+        <v>8.7137602430504252E-2</v>
+      </c>
+      <c r="AC11">
+        <v>-5.8249665624426221</v>
+      </c>
+    </row>
+    <row r="12" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12">
+        <v>-0.56166537386272619</v>
+      </c>
+      <c r="D12">
+        <v>9.5504898441980388E-2</v>
+      </c>
+      <c r="E12">
+        <v>-5.8810111630445867</v>
+      </c>
+      <c r="F12">
+        <v>0.54620000000000002</v>
+      </c>
+      <c r="G12">
+        <v>0.106935346079076</v>
+      </c>
+      <c r="H12">
+        <v>-3.9095966833634241</v>
+      </c>
+      <c r="I12">
+        <v>-0.59027914373242518</v>
+      </c>
+      <c r="J12">
+        <v>9.3811539239504596E-2</v>
+      </c>
+      <c r="K12">
+        <v>-6.2921805624084159</v>
+      </c>
+      <c r="L12">
+        <v>-0.41807407436507549</v>
+      </c>
+      <c r="M12">
+        <v>0.106935346079076</v>
+      </c>
+      <c r="N12">
+        <v>-3.9095966833634241</v>
+      </c>
+      <c r="O12">
+        <v>-0.50564434487211796</v>
+      </c>
+      <c r="P12">
+        <v>0.11882845580297149</v>
+      </c>
+      <c r="Q12">
+        <v>-4.2552462830159383</v>
+      </c>
+      <c r="R12">
+        <v>-0.58167549227004978</v>
+      </c>
+      <c r="S12">
+        <v>0.1231192882331619</v>
+      </c>
+      <c r="T12">
+        <v>-4.724487126407678</v>
+      </c>
+      <c r="U12">
+        <v>0.56999708699036256</v>
+      </c>
+      <c r="V12">
+        <v>0.13484109515071521</v>
+      </c>
+      <c r="W12">
+        <v>4.2271763393293611</v>
+      </c>
+      <c r="X12">
+        <v>-0.76153300451799422</v>
+      </c>
+      <c r="Y12">
+        <v>0.13910150386254511</v>
+      </c>
+      <c r="Z12">
+        <v>-5.4746568755325073</v>
+      </c>
+      <c r="AA12">
+        <v>-0.73010413800008644</v>
+      </c>
+      <c r="AB12">
+        <v>0.13700143201677281</v>
+      </c>
+      <c r="AC12">
+        <v>-5.3291715805620274</v>
+      </c>
+    </row>
+    <row r="13" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>-0.80677260661002015</v>
+      </c>
+      <c r="D13">
+        <v>5.889376726145671E-2</v>
+      </c>
+      <c r="E13">
+        <v>-13.698777377041999</v>
+      </c>
+      <c r="F13">
+        <v>-0.83020000000000005</v>
+      </c>
+      <c r="G13">
+        <v>6.1955306670808341E-2</v>
+      </c>
+      <c r="H13">
+        <v>-13.78665034190429</v>
+      </c>
+      <c r="I13">
+        <v>-0.87056148720070503</v>
+      </c>
+      <c r="J13">
+        <v>6.2198692208044568E-2</v>
+      </c>
+      <c r="K13">
+        <v>-13.99645967295932</v>
+      </c>
+      <c r="L13">
+        <v>-0.85415614989588473</v>
+      </c>
+      <c r="M13">
+        <v>6.1955306670808341E-2</v>
+      </c>
+      <c r="N13">
+        <v>-13.78665034190429</v>
+      </c>
+      <c r="O13">
+        <v>-0.99904558668252552</v>
+      </c>
+      <c r="P13">
+        <v>7.2919525241500388E-2</v>
+      </c>
+      <c r="Q13">
+        <v>-13.70065950613105</v>
+      </c>
+      <c r="R13">
+        <v>-1.132791350835713</v>
+      </c>
+      <c r="S13">
+        <v>7.7104850136980985E-2</v>
+      </c>
+      <c r="T13">
+        <v>-14.69157061875157</v>
+      </c>
+      <c r="U13">
+        <v>-1.2767852210729209</v>
+      </c>
+      <c r="V13">
+        <v>9.1659688329151084E-2</v>
+      </c>
+      <c r="W13">
+        <v>-13.929626473177271</v>
+      </c>
+      <c r="X13">
+        <v>-1.2683452231489409</v>
+      </c>
+      <c r="Y13">
+        <v>0.1019527470103478</v>
+      </c>
+      <c r="Z13">
+        <v>-12.440520342430879</v>
+      </c>
+      <c r="AA13">
+        <v>-1.330242206647223</v>
+      </c>
+      <c r="AB13">
+        <v>0.10347429232979689</v>
+      </c>
+      <c r="AC13">
+        <v>-12.85577486635451</v>
+      </c>
+    </row>
+    <row r="14" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14">
+        <v>-0.86174483846816607</v>
+      </c>
+      <c r="D14">
+        <v>5.8922634232687281E-2</v>
+      </c>
+      <c r="E14">
+        <v>-14.62502228031947</v>
+      </c>
+      <c r="F14">
+        <v>-0.76829999999999998</v>
+      </c>
+      <c r="G14">
+        <v>6.6612833123810139E-2</v>
+      </c>
+      <c r="H14">
+        <v>-13.56303267599314</v>
+      </c>
+      <c r="I14">
+        <v>-0.8279911237191907</v>
+      </c>
+      <c r="J14">
+        <v>6.7572689028281521E-2</v>
+      </c>
+      <c r="K14">
+        <v>-12.25333985706337</v>
+      </c>
+      <c r="L14">
+        <v>-0.90347203229871542</v>
+      </c>
+      <c r="M14">
+        <v>6.6612833123810139E-2</v>
+      </c>
+      <c r="N14">
+        <v>-13.56303267599314</v>
+      </c>
+      <c r="O14">
+        <v>-1.0761403824251969</v>
+      </c>
+      <c r="P14">
+        <v>6.990728390383856E-2</v>
+      </c>
+      <c r="Q14">
+        <v>-15.39382339479087</v>
+      </c>
+      <c r="R14">
+        <v>-0.97453780975154169</v>
+      </c>
+      <c r="S14">
+        <v>7.6595390645363151E-2</v>
+      </c>
+      <c r="T14">
+        <v>-12.723191324444761</v>
+      </c>
+      <c r="U14">
+        <v>-1.1058345902927591</v>
+      </c>
+      <c r="V14">
+        <v>8.899445286638423E-2</v>
+      </c>
+      <c r="W14">
+        <v>-12.42588222833453</v>
+      </c>
+      <c r="X14">
+        <v>-1.297014507435478</v>
+      </c>
+      <c r="Y14">
+        <v>0.1012611669136769</v>
+      </c>
+      <c r="Z14">
+        <v>-12.808607158765581</v>
+      </c>
+      <c r="AA14">
+        <v>-0.92370118751639785</v>
+      </c>
+      <c r="AB14">
+        <v>0.1015215808918654</v>
+      </c>
+      <c r="AC14">
+        <v>-9.0985697760190316</v>
+      </c>
+    </row>
+    <row r="15" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15">
+        <v>-0.56465120166629379</v>
+      </c>
+      <c r="D15">
+        <v>5.416507583533204E-2</v>
+      </c>
+      <c r="E15">
+        <v>-10.42463604007308</v>
+      </c>
+      <c r="F15">
+        <v>-0.55310000000000004</v>
+      </c>
+      <c r="G15">
+        <v>5.455425715403904E-2</v>
+      </c>
+      <c r="H15">
+        <v>-11.060235410339949</v>
+      </c>
+      <c r="I15">
+        <v>-0.56330427205650158</v>
+      </c>
+      <c r="J15">
+        <v>5.3098605096860013E-2</v>
+      </c>
+      <c r="K15">
+        <v>-10.60864538774508</v>
+      </c>
+      <c r="L15">
+        <v>-0.60338292675989391</v>
+      </c>
+      <c r="M15">
+        <v>5.455425715403904E-2</v>
+      </c>
+      <c r="N15">
+        <v>-11.060235410339949</v>
+      </c>
+      <c r="O15">
+        <v>-0.69712841702093586</v>
+      </c>
+      <c r="P15">
+        <v>6.4235563173033652E-2</v>
+      </c>
+      <c r="Q15">
+        <v>-10.85268630934325</v>
+      </c>
+      <c r="R15">
+        <v>-0.67508083724754664</v>
+      </c>
+      <c r="S15">
+        <v>6.4831648814703574E-2</v>
+      </c>
+      <c r="T15">
+        <v>-10.412828450144881</v>
+      </c>
+      <c r="U15">
+        <v>-0.80122571677348808</v>
+      </c>
+      <c r="V15">
+        <v>7.5646346267260883E-2</v>
+      </c>
+      <c r="W15">
+        <v>-10.591730550246711</v>
+      </c>
+      <c r="X15">
+        <v>-0.82854838740382308</v>
+      </c>
+      <c r="Y15">
+        <v>8.6312549742082773E-2</v>
+      </c>
+      <c r="Z15">
+        <v>-9.5993964942487828</v>
+      </c>
+      <c r="AA15">
+        <v>-0.82429868480373925</v>
+      </c>
+      <c r="AB15">
+        <v>8.6335186843513434E-2</v>
+      </c>
+      <c r="AC15">
+        <v>-9.5476562331163901</v>
+      </c>
+    </row>
+    <row r="16" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16">
+        <v>0.5157483212830245</v>
+      </c>
+      <c r="D16">
+        <v>0.1092662762682057</v>
+      </c>
+      <c r="E16">
+        <v>4.7201052227410516</v>
+      </c>
+      <c r="F16">
+        <v>0.52010000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.1196003334243759</v>
+      </c>
+      <c r="H16">
+        <v>3.7290535321169331</v>
+      </c>
+      <c r="I16">
+        <v>0.37453732364517311</v>
+      </c>
+      <c r="J16">
+        <v>0.12684796393885181</v>
+      </c>
+      <c r="K16">
+        <v>2.952647500323474</v>
+      </c>
+      <c r="L16">
+        <v>0.44599604579853191</v>
+      </c>
+      <c r="M16">
+        <v>0.1196003334243759</v>
+      </c>
+      <c r="N16">
+        <v>3.7290535321169331</v>
+      </c>
+      <c r="O16">
+        <v>0.63785755982649139</v>
+      </c>
+      <c r="P16">
+        <v>0.1126078132407882</v>
+      </c>
+      <c r="Q16">
+        <v>5.6644165397525894</v>
+      </c>
+      <c r="R16">
+        <v>0.42535590919769922</v>
+      </c>
+      <c r="S16">
+        <v>0.14236802093224041</v>
+      </c>
+      <c r="T16">
+        <v>2.9877208829091328</v>
+      </c>
+      <c r="U16">
+        <v>0.54095198060831307</v>
+      </c>
+      <c r="V16">
+        <v>0.15564010140044951</v>
+      </c>
+      <c r="W16">
+        <v>3.475659394595787</v>
+      </c>
+      <c r="X16">
+        <v>-0.76332288778690316</v>
+      </c>
+      <c r="Y16">
+        <v>0.14087756849527699</v>
+      </c>
+      <c r="Z16">
+        <v>-5.4183422949445212</v>
+      </c>
+      <c r="AA16">
+        <v>0.34197447123510061</v>
+      </c>
+      <c r="AB16">
+        <v>0.20955996751186429</v>
+      </c>
+      <c r="AC16">
+        <v>1.631869270144545</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17">
+        <v>-0.46227432665675422</v>
+      </c>
+      <c r="D17">
+        <v>4.2547474604491577E-2</v>
+      </c>
+      <c r="E17">
+        <v>-10.86490634177272</v>
+      </c>
+      <c r="F17">
+        <v>-0.46079999999999999</v>
+      </c>
+      <c r="G17">
+        <v>4.2995655058216377E-2</v>
+      </c>
+      <c r="H17">
+        <v>-11.19638031894803</v>
+      </c>
+      <c r="I17">
+        <v>-0.48313502209356202</v>
+      </c>
+      <c r="J17">
+        <v>4.2810049209214669E-2</v>
+      </c>
+      <c r="K17">
+        <v>-11.28555166410716</v>
+      </c>
+      <c r="L17">
+        <v>-0.48139570609409221</v>
+      </c>
+      <c r="M17">
+        <v>4.2995655058216377E-2</v>
+      </c>
+      <c r="N17">
+        <v>-11.19638031894803</v>
+      </c>
+      <c r="O17">
+        <v>-0.54111350615555143</v>
+      </c>
+      <c r="P17">
+        <v>5.0423553385355972E-2</v>
+      </c>
+      <c r="Q17">
+        <v>-10.73136401197584</v>
+      </c>
+      <c r="R17">
+        <v>-0.5582474248657332</v>
+      </c>
+      <c r="S17">
+        <v>5.5318184740961993E-2</v>
+      </c>
+      <c r="T17">
+        <v>-10.09157165007915</v>
+      </c>
+      <c r="U17">
+        <v>-0.61136243589197348</v>
+      </c>
+      <c r="V17">
+        <v>6.0434729945735552E-2</v>
+      </c>
+      <c r="W17">
+        <v>-10.11607789827003</v>
+      </c>
+      <c r="X17">
+        <v>-0.6262084538235857</v>
+      </c>
+      <c r="Y17">
+        <v>6.6765352357373312E-2</v>
+      </c>
+      <c r="Z17">
+        <v>-9.3792428514672501</v>
+      </c>
+      <c r="AA17">
+        <v>-0.62610091288523395</v>
+      </c>
+      <c r="AB17">
+        <v>7.0137327404801456E-2</v>
+      </c>
+      <c r="AC17">
+        <v>-8.9267860075656724</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>0.62652206272601729</v>
+      </c>
+      <c r="D18">
+        <v>6.5550613741023514E-2</v>
+      </c>
+      <c r="E18">
+        <v>9.5578367153246226</v>
+      </c>
+      <c r="F18">
+        <v>0.6724</v>
+      </c>
+      <c r="G18">
+        <v>6.6473923610018776E-2</v>
+      </c>
+      <c r="H18">
+        <v>9.6034297865423657</v>
+      </c>
+      <c r="I18">
+        <v>0.60273830476913048</v>
+      </c>
+      <c r="J18">
+        <v>6.8642692878955316E-2</v>
+      </c>
+      <c r="K18">
+        <v>8.7808079708061655</v>
+      </c>
+      <c r="L18">
+        <v>0.63837765802479618</v>
+      </c>
+      <c r="M18">
+        <v>6.6473923610018776E-2</v>
+      </c>
+      <c r="N18">
+        <v>9.6034297865423657</v>
+      </c>
+      <c r="O18">
+        <v>0.77076730283363837</v>
+      </c>
+      <c r="P18">
+        <v>7.2243637068421601E-2</v>
+      </c>
+      <c r="Q18">
+        <v>10.66899915495185</v>
+      </c>
+      <c r="R18">
+        <v>0.83454958653342071</v>
+      </c>
+      <c r="S18">
+        <v>7.6509566241676097E-2</v>
+      </c>
+      <c r="T18">
+        <v>10.907780915882739</v>
+      </c>
+      <c r="U18">
+        <v>0.79408245282003576</v>
+      </c>
+      <c r="V18">
+        <v>9.0207304261155433E-2</v>
+      </c>
+      <c r="W18">
+        <v>8.8028620223604115</v>
+      </c>
+      <c r="X18">
+        <v>0.83050919271363788</v>
+      </c>
+      <c r="Y18">
+        <v>9.2971748109908353E-2</v>
+      </c>
+      <c r="Z18">
+        <v>8.9329200493448333</v>
+      </c>
+      <c r="AA18">
+        <v>0.84433063893526172</v>
+      </c>
+      <c r="AB18">
+        <v>9.9764365882862166E-2</v>
+      </c>
+      <c r="AC18">
+        <v>8.4632486906860951</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>-0.13916009487782399</v>
+      </c>
+      <c r="D19">
+        <v>3.975405412674788E-2</v>
+      </c>
+      <c r="E19">
+        <v>-3.5005258692393939</v>
+      </c>
+      <c r="F19">
+        <v>-0.1237</v>
+      </c>
+      <c r="G19">
+        <v>4.0687926044609343E-2</v>
+      </c>
+      <c r="H19">
+        <v>-3.6735312409943401</v>
+      </c>
+      <c r="I19">
+        <v>-0.13838719903513619</v>
+      </c>
+      <c r="J19">
+        <v>3.9066966234472728E-2</v>
+      </c>
+      <c r="K19">
+        <v>-3.5423072834619842</v>
+      </c>
+      <c r="L19">
+        <v>-0.1494683674561397</v>
+      </c>
+      <c r="M19">
+        <v>4.0687926044609343E-2</v>
+      </c>
+      <c r="N19">
+        <v>-3.6735312409943401</v>
+      </c>
+      <c r="O19">
+        <v>-0.2044215234155794</v>
+      </c>
+      <c r="P19">
+        <v>4.5555660761679953E-2</v>
+      </c>
+      <c r="Q19">
+        <v>-4.487291370549773</v>
+      </c>
+      <c r="R19">
+        <v>-0.20961845237162441</v>
+      </c>
+      <c r="S19">
+        <v>4.9412626448283849E-2</v>
+      </c>
+      <c r="T19">
+        <v>-4.2422042186123194</v>
+      </c>
+      <c r="U19">
+        <v>-0.27471500490879491</v>
+      </c>
+      <c r="V19">
+        <v>5.8134525107308078E-2</v>
+      </c>
+      <c r="W19">
+        <v>-4.7255052724987427</v>
+      </c>
+      <c r="X19">
+        <v>-0.26681555689958492</v>
+      </c>
+      <c r="Y19">
+        <v>6.391160387970117E-2</v>
+      </c>
+      <c r="Z19">
+        <v>-4.1747592096390438</v>
+      </c>
+      <c r="AA19">
+        <v>-0.21957871589210601</v>
+      </c>
+      <c r="AB19">
+        <v>6.4659014805836995E-2</v>
+      </c>
+      <c r="AC19">
+        <v>-3.3959489879558729</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <v>-0.4769212682099539</v>
+      </c>
+      <c r="D20">
+        <v>6.9779849160298377E-2</v>
+      </c>
+      <c r="E20">
+        <v>-6.8346560496909303</v>
+      </c>
+      <c r="F20">
+        <v>-0.46339999999999998</v>
+      </c>
+      <c r="G20">
+        <v>7.6531552329075409E-2</v>
+      </c>
+      <c r="H20">
+        <v>-5.8659708857659467</v>
+      </c>
+      <c r="I20">
+        <v>-0.32208363554788982</v>
+      </c>
+      <c r="J20">
+        <v>9.358672146214346E-2</v>
+      </c>
+      <c r="K20">
+        <v>-3.4415527172642228</v>
+      </c>
+      <c r="L20">
+        <v>-0.44893185780482942</v>
+      </c>
+      <c r="M20">
+        <v>7.6531552329075409E-2</v>
+      </c>
+      <c r="N20">
+        <v>-5.8659708857659467</v>
+      </c>
+      <c r="O20">
+        <v>-0.37210117782308549</v>
+      </c>
+      <c r="P20">
+        <v>9.1296173350299131E-2</v>
+      </c>
+      <c r="Q20">
+        <v>-4.0757587549190131</v>
+      </c>
+      <c r="R20">
+        <v>-0.39739186320744468</v>
+      </c>
+      <c r="S20">
+        <v>9.722221179440356E-2</v>
+      </c>
+      <c r="T20">
+        <v>-4.0874596028303882</v>
+      </c>
+      <c r="U20">
+        <v>0.57852917637252654</v>
+      </c>
+      <c r="V20">
+        <v>0.1006335837196089</v>
+      </c>
+      <c r="W20">
+        <v>5.7488678728212417</v>
+      </c>
+      <c r="X20">
+        <v>-0.56678388230644339</v>
+      </c>
+      <c r="Y20">
+        <v>0.102454589262731</v>
+      </c>
+      <c r="Z20">
+        <v>-5.5320497245174902</v>
+      </c>
+      <c r="AA20">
+        <v>-0.4209005509194037</v>
+      </c>
+      <c r="AB20">
+        <v>0.13633919491139079</v>
+      </c>
+      <c r="AC20">
+        <v>-3.087157373878834</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21">
+        <v>0.18860864748547601</v>
+      </c>
+      <c r="D21">
+        <v>4.0485254168670007E-2</v>
+      </c>
+      <c r="E21">
+        <v>4.6586998490782134</v>
+      </c>
+      <c r="F21">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="G21">
+        <v>4.2214253075917182E-2</v>
+      </c>
+      <c r="H21">
+        <v>4.6424837827834651</v>
+      </c>
+      <c r="I21">
+        <v>0.17474195364971179</v>
+      </c>
+      <c r="J21">
+        <v>4.1155976252330459E-2</v>
+      </c>
+      <c r="K21">
+        <v>4.2458464009784489</v>
+      </c>
+      <c r="L21">
+        <v>0.19597898530726249</v>
+      </c>
+      <c r="M21">
+        <v>4.2214253075917182E-2</v>
+      </c>
+      <c r="N21">
+        <v>4.6424837827834651</v>
+      </c>
+      <c r="O21">
+        <v>0.19379862265822889</v>
+      </c>
+      <c r="P21">
+        <v>4.7014846590693077E-2</v>
+      </c>
+      <c r="Q21">
+        <v>4.1220728495707286</v>
+      </c>
+      <c r="R21">
+        <v>0.18325635656019251</v>
+      </c>
+      <c r="S21">
+        <v>5.0323731607816953E-2</v>
+      </c>
+      <c r="T21">
+        <v>3.6415494381129458</v>
+      </c>
+      <c r="U21">
+        <v>0.17987210627754949</v>
+      </c>
+      <c r="V21">
+        <v>5.8757109244083172E-2</v>
+      </c>
+      <c r="W21">
+        <v>3.0612824318899339</v>
+      </c>
+      <c r="X21">
+        <v>0.2349273661384145</v>
+      </c>
+      <c r="Y21">
+        <v>6.3625785568532073E-2</v>
+      </c>
+      <c r="Z21">
+        <v>3.692329517650851</v>
+      </c>
+      <c r="AA21">
+        <v>0.23712479220903779</v>
+      </c>
+      <c r="AB21">
+        <v>6.6601039455895822E-2</v>
+      </c>
+      <c r="AC21">
+        <v>3.5603767470636152</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22">
+        <v>0.73664507874299456</v>
+      </c>
+      <c r="D22">
+        <v>5.7537492039334073E-2</v>
+      </c>
+      <c r="E22">
+        <v>12.80287083488807</v>
+      </c>
+      <c r="F22">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="G22">
+        <v>6.0874623547277518E-2</v>
+      </c>
+      <c r="H22">
+        <v>12.306958822403599</v>
+      </c>
+      <c r="I22">
+        <v>0.70006699541501316</v>
+      </c>
+      <c r="J22">
+        <v>6.223852483125572E-2</v>
+      </c>
+      <c r="K22">
+        <v>11.24812963213814</v>
+      </c>
+      <c r="L22">
+        <v>0.74918148532566509</v>
+      </c>
+      <c r="M22">
+        <v>6.0874623547277518E-2</v>
+      </c>
+      <c r="N22">
+        <v>12.306958822403599</v>
+      </c>
+      <c r="O22">
+        <v>0.82480947035471275</v>
+      </c>
+      <c r="P22">
+        <v>6.6676069671759083E-2</v>
+      </c>
+      <c r="Q22">
+        <v>12.37039727169258</v>
+      </c>
+      <c r="R22">
+        <v>0.85023340050397189</v>
+      </c>
+      <c r="S22">
+        <v>7.3630193681123807E-2</v>
+      </c>
+      <c r="T22">
+        <v>11.54734705963353</v>
+      </c>
+      <c r="U22">
+        <v>-0.9692606733157183</v>
+      </c>
+      <c r="V22">
+        <v>8.0069578904450323E-2</v>
+      </c>
+      <c r="W22">
+        <v>-12.105230058376719</v>
+      </c>
+      <c r="X22">
+        <v>0.96792761620625212</v>
+      </c>
+      <c r="Y22">
+        <v>9.1748197591309213E-2</v>
+      </c>
+      <c r="Z22">
+        <v>10.5498270442093</v>
+      </c>
+      <c r="AA22">
+        <v>0.87725659161428793</v>
+      </c>
+      <c r="AB22">
+        <v>9.4817523127104258E-2</v>
+      </c>
+      <c r="AC22">
+        <v>9.2520513369486856</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23">
+        <v>0.23801428957491871</v>
+      </c>
+      <c r="D23">
+        <v>4.0801309985146472E-2</v>
+      </c>
+      <c r="E23">
+        <v>5.8334962691532857</v>
+      </c>
+      <c r="F23">
+        <v>0.23330000000000001</v>
+      </c>
+      <c r="G23">
+        <v>4.218960487525255E-2</v>
+      </c>
+      <c r="H23">
+        <v>5.8858401359827583</v>
+      </c>
+      <c r="I23">
+        <v>0.22775178960193851</v>
+      </c>
+      <c r="J23">
+        <v>4.2562560293243443E-2</v>
+      </c>
+      <c r="K23">
+        <v>5.3509889450445653</v>
+      </c>
+      <c r="L23">
+        <v>0.24832126969601531</v>
+      </c>
+      <c r="M23">
+        <v>4.218960487525255E-2</v>
+      </c>
+      <c r="N23">
+        <v>5.8858401359827583</v>
+      </c>
+      <c r="O23">
+        <v>0.25916614175807762</v>
+      </c>
+      <c r="P23">
+        <v>4.8556547365706651E-2</v>
+      </c>
+      <c r="Q23">
+        <v>5.337408770153111</v>
+      </c>
+      <c r="R23">
+        <v>0.25725191636577949</v>
+      </c>
+      <c r="S23">
+        <v>5.2806428932490247E-2</v>
+      </c>
+      <c r="T23">
+        <v>4.8716022190150401</v>
+      </c>
+      <c r="U23">
+        <v>0.23803039457881969</v>
+      </c>
+      <c r="V23">
+        <v>5.9985064843646838E-2</v>
+      </c>
+      <c r="W23">
+        <v>3.9681609947285081</v>
+      </c>
+      <c r="X23">
+        <v>0.23826006306726</v>
+      </c>
+      <c r="Y23">
+        <v>6.6135844276105249E-2</v>
+      </c>
+      <c r="Z23">
+        <v>3.6025859452639191</v>
+      </c>
+      <c r="AA23">
+        <v>0.27362634707668437</v>
+      </c>
+      <c r="AB23">
+        <v>7.0441014728753179E-2</v>
+      </c>
+      <c r="AC23">
+        <v>3.8844748067633019</v>
+      </c>
+    </row>
+    <row r="24" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C24">
+        <v>-0.98849191779529266</v>
+      </c>
+      <c r="D24">
+        <v>5.0563776082676488E-2</v>
+      </c>
+      <c r="E24">
+        <v>-19.549408576191311</v>
+      </c>
+      <c r="F24">
+        <v>-0.97250000000000003</v>
+      </c>
+      <c r="G24">
+        <v>5.1694727866867941E-2</v>
+      </c>
+      <c r="H24">
+        <v>-19.437158594055539</v>
+      </c>
+      <c r="I24">
+        <v>-1.020990926264876</v>
+      </c>
+      <c r="J24">
+        <v>5.2150456397438247E-2</v>
+      </c>
+      <c r="K24">
+        <v>-19.57779465023108</v>
+      </c>
+      <c r="L24">
+        <v>-1.004798624024855</v>
+      </c>
+      <c r="M24">
+        <v>5.1694727866867941E-2</v>
+      </c>
+      <c r="N24">
+        <v>-19.437158594055539</v>
+      </c>
+      <c r="O24">
+        <v>-1.1193141983709161</v>
+      </c>
+      <c r="P24">
+        <v>6.0445811566005189E-2</v>
+      </c>
+      <c r="Q24">
+        <v>-18.517646953067288</v>
+      </c>
+      <c r="R24">
+        <v>-1.1521615910478979</v>
+      </c>
+      <c r="S24">
+        <v>6.4722309427492311E-2</v>
+      </c>
+      <c r="T24">
+        <v>-17.801614331124131</v>
+      </c>
+      <c r="U24">
+        <v>-1.2406471816915059</v>
+      </c>
+      <c r="V24">
+        <v>7.594027111874263E-2</v>
+      </c>
+      <c r="W24">
+        <v>-16.337144487561691</v>
+      </c>
+      <c r="X24">
+        <v>-1.2903364842135361</v>
+      </c>
+      <c r="Y24">
+        <v>8.4886659184324517E-2</v>
+      </c>
+      <c r="Z24">
+        <v>-15.200698161670781</v>
+      </c>
+      <c r="AA24">
+        <v>-1.280629310401743</v>
+      </c>
+      <c r="AB24">
+        <v>8.9769385959016276E-2</v>
+      </c>
+      <c r="AC24">
+        <v>-14.265768855614169</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25">
+        <v>0.92006072384306992</v>
+      </c>
+      <c r="D25">
+        <v>3.8907056605780047E-2</v>
+      </c>
+      <c r="E25">
+        <v>23.64765685478211</v>
+      </c>
+      <c r="F25">
+        <v>0.94259999999999999</v>
+      </c>
+      <c r="G25">
+        <v>4.0771444876447939E-2</v>
+      </c>
+      <c r="H25">
+        <v>23.44068725121528</v>
+      </c>
+      <c r="I25">
+        <v>0.92952253387325345</v>
+      </c>
+      <c r="J25">
+        <v>3.9686629562530953E-2</v>
+      </c>
+      <c r="K25">
+        <v>23.42155391171935</v>
+      </c>
+      <c r="L25">
+        <v>0.95571068812897975</v>
+      </c>
+      <c r="M25">
+        <v>4.0771444876447939E-2</v>
+      </c>
+      <c r="N25">
+        <v>23.44068725121528</v>
+      </c>
+      <c r="O25">
+        <v>0.90052714560756519</v>
+      </c>
+      <c r="P25">
+        <v>4.2986944348040998E-2</v>
+      </c>
+      <c r="Q25">
+        <v>20.94885224491664</v>
+      </c>
+      <c r="R25">
+        <v>0.91097638131414138</v>
+      </c>
+      <c r="S25">
+        <v>4.5512742248418912E-2</v>
+      </c>
+      <c r="T25">
+        <v>20.01585350190118</v>
+      </c>
+      <c r="U25">
+        <v>0.86110797010842</v>
+      </c>
+      <c r="V25">
+        <v>4.7475790638349162E-2</v>
+      </c>
+      <c r="W25">
+        <v>18.137833167813518</v>
+      </c>
+      <c r="X25">
+        <v>0.83767159306622341</v>
+      </c>
+      <c r="Y25">
+        <v>4.9720650772606359E-2</v>
+      </c>
+      <c r="Z25">
+        <v>16.84755891263876</v>
+      </c>
+      <c r="AA25">
+        <v>0.84111134545299793</v>
+      </c>
+      <c r="AB25">
+        <v>5.2548323771881227E-2</v>
+      </c>
+      <c r="AC25">
+        <v>16.006435316649991</v>
+      </c>
+    </row>
+    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26">
+        <v>0.94259473976841657</v>
+      </c>
+      <c r="D26">
+        <v>3.9582928338855732E-2</v>
+      </c>
+      <c r="E26">
+        <v>23.8131633844568</v>
+      </c>
+      <c r="F26">
+        <v>0.94779999999999998</v>
+      </c>
+      <c r="G26">
+        <v>4.4220529921789688E-2</v>
+      </c>
+      <c r="H26">
+        <v>22.337420421519209</v>
+      </c>
+      <c r="I26">
+        <v>0.94403405651837313</v>
+      </c>
+      <c r="J26">
+        <v>4.0847632005852418E-2</v>
+      </c>
+      <c r="K26">
+        <v>23.111108530920891</v>
+      </c>
+      <c r="L26">
+        <v>0.98777256812538639</v>
+      </c>
+      <c r="M26">
+        <v>4.4220529921789688E-2</v>
+      </c>
+      <c r="N26">
+        <v>22.337420421519209</v>
+      </c>
+      <c r="O26">
+        <v>0.97840613350107786</v>
+      </c>
+      <c r="P26">
+        <v>4.8731559933178598E-2</v>
+      </c>
+      <c r="Q26">
+        <v>20.077463862077931</v>
+      </c>
+      <c r="R26">
+        <v>0.97997341652916936</v>
+      </c>
+      <c r="S26">
+        <v>5.1724805430680899E-2</v>
+      </c>
+      <c r="T26">
+        <v>18.945908222747839</v>
+      </c>
+      <c r="U26">
+        <v>0.90269771447367952</v>
+      </c>
+      <c r="V26">
+        <v>5.2568536115855623E-2</v>
+      </c>
+      <c r="W26">
+        <v>17.171825224203069</v>
+      </c>
+      <c r="X26">
+        <v>0.92894467230683919</v>
+      </c>
+      <c r="Y26">
+        <v>5.9355272255189391E-2</v>
+      </c>
+      <c r="Z26">
+        <v>15.650583966879569</v>
+      </c>
+      <c r="AA26">
+        <v>0.90173253666886444</v>
+      </c>
+      <c r="AB26">
+        <v>6.0040942719563027E-2</v>
+      </c>
+      <c r="AC26">
+        <v>15.018627220439271</v>
+      </c>
+    </row>
+    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C27">
+        <v>0.45213751483225451</v>
+      </c>
+      <c r="F27">
+        <v>0.45003503016175472</v>
+      </c>
+      <c r="I27">
+        <v>0.45428505834326199</v>
+      </c>
+      <c r="L27">
+        <v>0.45003503016175472</v>
+      </c>
+      <c r="O27">
+        <v>0.44325561626105969</v>
+      </c>
+      <c r="R27">
+        <v>0.43382447066352858</v>
+      </c>
+      <c r="U27">
+        <v>0.42782557956491701</v>
+      </c>
+      <c r="X27">
+        <v>0.42023104237548281</v>
+      </c>
+      <c r="AA27">
+        <v>0.41956504010603451</v>
+      </c>
+    </row>
+    <row r="28" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C28">
+        <v>0.25</v>
+      </c>
+      <c r="F28">
+        <v>0.25</v>
+      </c>
+      <c r="I28">
+        <v>0.25</v>
+      </c>
+      <c r="L28">
+        <v>0.25</v>
+      </c>
+      <c r="O28">
+        <v>0.25</v>
+      </c>
+      <c r="R28">
+        <v>0.25</v>
+      </c>
+      <c r="U28">
+        <v>0.25</v>
+      </c>
+      <c r="X28">
+        <v>0.25</v>
+      </c>
+      <c r="AA28">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29">
+        <v>0.19861042938130491</v>
+      </c>
+      <c r="F29">
+        <v>0.20252241570836571</v>
+      </c>
+      <c r="I29">
+        <v>0.2003597079540623</v>
+      </c>
+      <c r="L29">
+        <v>0.20252241570836571</v>
+      </c>
+      <c r="O29">
+        <v>0.20235930546861519</v>
+      </c>
+      <c r="R29">
+        <v>0.2041323884814768</v>
+      </c>
+      <c r="U29">
+        <v>0.20558301267803081</v>
+      </c>
+      <c r="X29">
+        <v>0.2043172835368034</v>
+      </c>
+      <c r="AA29">
+        <v>0.20497375192168901</v>
+      </c>
+    </row>
+    <row r="30" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C30">
+        <v>0.28983051589032</v>
+      </c>
+      <c r="F30">
+        <v>0.29384523886319708</v>
+      </c>
+      <c r="I30">
+        <v>0.29516682493656021</v>
+      </c>
+      <c r="L30">
+        <v>0.29384523886319708</v>
+      </c>
+      <c r="O30">
+        <v>0.29450148346711291</v>
+      </c>
+      <c r="R30">
+        <v>0.29582698584818862</v>
+      </c>
+      <c r="U30">
+        <v>0.29340299297678069</v>
+      </c>
+      <c r="X30">
+        <v>0.29483887550565752</v>
+      </c>
+      <c r="AA30">
+        <v>0.29653914100016099</v>
+      </c>
+    </row>
+    <row r="31" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31">
+        <v>0.43670311585177651</v>
+      </c>
+      <c r="F31">
+        <v>0.42951474794719668</v>
+      </c>
+      <c r="I31">
+        <v>0.43963126201625341</v>
+      </c>
+      <c r="L31">
+        <v>0.42951474794719668</v>
+      </c>
+      <c r="O31">
+        <v>0.41665480404699612</v>
+      </c>
+      <c r="R31">
+        <v>0.40856536104403463</v>
+      </c>
+      <c r="U31">
+        <v>0.40346224734200342</v>
+      </c>
+      <c r="X31">
+        <v>0.40285831513919401</v>
+      </c>
+      <c r="AA31">
+        <v>0.39851147969254419</v>
+      </c>
+    </row>
+    <row r="32" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>274</v>
+      </c>
+      <c r="C32">
+        <v>0.83592494720213784</v>
+      </c>
+      <c r="F32">
+        <v>0.82894308068514522</v>
+      </c>
+      <c r="I32">
+        <v>0.83491939131920412</v>
+      </c>
+      <c r="L32">
+        <v>0.82894308068514522</v>
+      </c>
+      <c r="O32">
+        <v>0.82367213067269129</v>
+      </c>
+      <c r="R32">
+        <v>0.72113774836292932</v>
+      </c>
+      <c r="U32">
+        <v>0.69984477546889035</v>
+      </c>
+      <c r="X32">
+        <v>0.67604357802841175</v>
+      </c>
+      <c r="AA32">
+        <v>0.67521405059926165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33">
+        <v>0.84393807634712736</v>
+      </c>
+      <c r="F33">
+        <v>0.83642291481206787</v>
+      </c>
+      <c r="I33">
+        <v>0.84209478523775394</v>
+      </c>
+      <c r="L33">
+        <v>0.83642291481206787</v>
+      </c>
+      <c r="O33">
+        <v>0.83522440594300562</v>
+      </c>
+      <c r="R33">
+        <v>0.82218360990271322</v>
+      </c>
+      <c r="U33">
+        <v>0.82452387783857162</v>
+      </c>
+      <c r="X33">
+        <v>0.81731606237085086</v>
+      </c>
+      <c r="AA33">
+        <v>0.81797779845717067</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" t="s">
+        <v>279</v>
+      </c>
+      <c r="E38" t="s">
+        <v>278</v>
+      </c>
+      <c r="F38" t="s">
+        <v>281</v>
+      </c>
+      <c r="G38" t="s">
+        <v>280</v>
+      </c>
+      <c r="H38" t="s">
+        <v>277</v>
+      </c>
+      <c r="I38" t="s">
+        <v>282</v>
+      </c>
+      <c r="J38" t="s">
+        <v>283</v>
+      </c>
+      <c r="K38" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="str">
+        <f>_xlfn.CONCAT(ROUND(C3,3)," ",IF(ABS(E3)&gt;2.01,"***",IF(ABS(E3)&gt;1.96,"**",IF(ABS(E3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(D3,3),")")</f>
+        <v>1.487 ***
+(0.09)</v>
+      </c>
+      <c r="D39" t="str">
+        <f>_xlfn.CONCAT(ROUND(F3,3)," ",IF(ABS(H3)&gt;2.01,"***",IF(ABS(H3)&gt;1.96,"**",IF(ABS(H3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(G3,3),")")</f>
+        <v>1.51 ***
+(0.093)</v>
+      </c>
+      <c r="E39" t="str">
+        <f>_xlfn.CONCAT(ROUND(I3,3)," ",IF(ABS(K3)&gt;2.01,"***",IF(ABS(K3)&gt;1.96,"**",IF(ABS(K3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(J3,3),")")</f>
+        <v>1.587 ***
+(0.094)</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" ref="F39:F62" si="0">_xlfn.CONCAT(ROUND(L3,3)," ",IF(ABS(N3)&gt;2.01,"***",IF(ABS(N3)&gt;1.96,"**",IF(ABS(N3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(M3,3),")")</f>
+        <v>1.7 ***
+(0.093)</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" ref="G39:G62" si="1">_xlfn.CONCAT(ROUND(O3,3)," ",IF(ABS(Q3)&gt;2.01,"***",IF(ABS(Q3)&gt;1.96,"**",IF(ABS(Q3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(P3,3),")")</f>
+        <v>1.944 ***
+(0.106)</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" ref="H39:H62" si="2">_xlfn.CONCAT(ROUND(R3,3)," ",IF(ABS(T3)&gt;2.01,"***",IF(ABS(T3)&gt;1.96,"**",IF(ABS(T3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(S3,3),")")</f>
+        <v>1.981 ***
+(0.115)</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" ref="I39:I62" si="3">_xlfn.CONCAT(ROUND(U3,3)," ",IF(ABS(W3)&gt;2.01,"***",IF(ABS(W3)&gt;1.96,"**",IF(ABS(W3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(V3,3),")")</f>
+        <v>2.373 ***
+(0.133)</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" ref="J39:J62" si="4">_xlfn.CONCAT(ROUND(X3,3)," ",IF(ABS(Z3)&gt;2.01,"***",IF(ABS(Z3)&gt;1.96,"**",IF(ABS(Z3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(Y3,3),")")</f>
+        <v>2.426 ***
+(0.145)</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" ref="K39:K62" si="5">_xlfn.CONCAT(ROUND(AA3,3)," ",IF(ABS(AC3)&gt;2.01,"***",IF(ABS(AC3)&gt;1.96,"**",IF(ABS(AC3)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(AB3,3),")")</f>
+        <v>2.532 ***
+(0.16)</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" ref="C40:C62" si="6">_xlfn.CONCAT(ROUND(C4,3)," ",IF(ABS(E4)&gt;2.01,"***",IF(ABS(E4)&gt;1.96,"**",IF(ABS(E4)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(D4,3),")")</f>
+        <v>2.119 ***
+(0.102)</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" ref="D40:D62" si="7">_xlfn.CONCAT(ROUND(F4,3)," ",IF(ABS(H4)&gt;2.01,"***",IF(ABS(H4)&gt;1.96,"**",IF(ABS(H4)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(G4,3),")")</f>
+        <v>2.085 ***
+(0.102)</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" ref="E40:E62" si="8">_xlfn.CONCAT(ROUND(I4,3)," ",IF(ABS(K4)&gt;2.01,"***",IF(ABS(K4)&gt;1.96,"**",IF(ABS(K4)&gt;1.69,"*",""))),CHAR(10),"(",ROUND(J4,3),")")</f>
+        <v>2.136 ***
+(0.105)</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>2.041 ***
+(0.102)</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="1"/>
+        <v>1.965 ***
+(0.11)</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="2"/>
+        <v>2.013 ***
+(0.119)</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="3"/>
+        <v>1.937 ***
+(0.13)</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="4"/>
+        <v>1.961 ***
+(0.149)</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="5"/>
+        <v>1.884 ***
+(0.149)</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="6"/>
+        <v>2.101 ***
+(0.102)</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="7"/>
+        <v>2.101 ***
+(0.106)</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="8"/>
+        <v>2.172 ***
+(0.106)</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>2.173 ***
+(0.106)</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="1"/>
+        <v>2.49 ***
+(0.121)</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="2"/>
+        <v>2.681 ***
+(0.13)</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="3"/>
+        <v>2.873 ***
+(0.147)</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="4"/>
+        <v>2.944 ***
+(0.166)</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="5"/>
+        <v>2.988 ***
+(0.174)</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="6"/>
+        <v>-2.79 ***
+(0.117)</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="7"/>
+        <v>-2.768 ***
+(0.118)</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="8"/>
+        <v>-2.812 ***
+(0.121)</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>-2.783 ***
+(0.118)</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="1"/>
+        <v>-2.638 ***
+(0.128)</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="2"/>
+        <v>-2.48 ***
+(0.126)</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="3"/>
+        <v>-2.536 ***
+(0.14)</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="4"/>
+        <v>-2.51 ***
+(0.156)</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="5"/>
+        <v>-2.359 ***
+(0.154)</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="6"/>
+        <v>5.303 ***
+(0.202)</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="7"/>
+        <v>5.261 ***
+(0.203)</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="8"/>
+        <v>5.452 ***
+(0.214)</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>5.228 ***
+(0.203)</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="1"/>
+        <v>5.758 ***
+(0.248)</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="2"/>
+        <v>5.771 ***
+(0.26)</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="3"/>
+        <v>6.428 ***
+(0.31)</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="4"/>
+        <v>6.284 ***
+(0.328)</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="5"/>
+        <v>6.374 ***
+(0.36)</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="6"/>
+        <v>-4.083 ***
+(0.162)</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="7"/>
+        <v>-4.125 ***
+(0.161)</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="8"/>
+        <v>-4.252 ***
+(0.172)</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>-3.979 ***
+(0.161)</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="1"/>
+        <v>-4.123 ***
+(0.187)</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="2"/>
+        <v>-4.039 ***
+(0.194)</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="3"/>
+        <v>-4.232 ***
+(0.234)</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="4"/>
+        <v>-3.88 ***
+(0.238)</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="5"/>
+        <v>-4.259 ***
+(0.275)</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>276</v>
+      </c>
+      <c r="B45" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>-5.917 ***
+(0.69)</v>
+      </c>
+      <c r="D45" s="55" t="str">
+        <f t="shared" si="7"/>
+        <v>-3.696 ***
+(0.359)</v>
+      </c>
+      <c r="E45" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>-3.515 ***
+(0.441)</v>
+      </c>
+      <c r="F45" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v>-2.315 ***
+(0.359)</v>
+      </c>
+      <c r="G45" s="55" t="str">
+        <f t="shared" si="1"/>
+        <v>-1.632 ***
+(0.313)</v>
+      </c>
+      <c r="H45" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>-1.083 ***
+(0.294)</v>
+      </c>
+      <c r="I45" s="55" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.421 
+(0.253)</v>
+      </c>
+      <c r="J45" s="55" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.346 
+(0.268)</v>
+      </c>
+      <c r="K45" s="55" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.323 
+(0.268)</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="6"/>
+        <v>-6.309 ***
+(0.42)</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="7"/>
+        <v>4.944 ***
+(0.2)</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="8"/>
+        <v>-4.964 ***
+(0.276)</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>-3.733 ***
+(0.2)</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="1"/>
+        <v>-3.492 ***
+(0.18)</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="2"/>
+        <v>3.141 ***
+(0.169)</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="3"/>
+        <v>2.647 ***
+(0.147)</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="4"/>
+        <v>2.531 ***
+(0.147)</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="5"/>
+        <v>-2.496 ***
+(0.141)</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.367 ***
+(0.053)</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.354 ***
+(0.054)</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.388 ***
+(0.055)</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.384 ***
+(0.054)</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.455 ***
+(0.06)</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.459 ***
+(0.067)</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.512 ***
+(0.074)</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.542 ***
+(0.083)</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.508 ***
+(0.087)</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.562 ***
+(0.096)</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="7"/>
+        <v>0.546 ***
+(0.107)</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.59 ***
+(0.094)</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.418 ***
+(0.107)</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.506 ***
+(0.119)</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.582 ***
+(0.123)</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="3"/>
+        <v>0.57 ***
+(0.135)</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.762 ***
+(0.139)</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.73 ***
+(0.137)</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.807 ***
+(0.059)</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.83 ***
+(0.062)</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.871 ***
+(0.062)</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.854 ***
+(0.062)</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.999 ***
+(0.073)</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="2"/>
+        <v>-1.133 ***
+(0.077)</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="3"/>
+        <v>-1.277 ***
+(0.092)</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="4"/>
+        <v>-1.268 ***
+(0.102)</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="5"/>
+        <v>-1.33 ***
+(0.103)</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.862 ***
+(0.059)</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.768 ***
+(0.067)</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.828 ***
+(0.068)</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.903 ***
+(0.067)</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>-1.076 ***
+(0.07)</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.975 ***
+(0.077)</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="3"/>
+        <v>-1.106 ***
+(0.089)</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="4"/>
+        <v>-1.297 ***
+(0.101)</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.924 ***
+(0.102)</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.565 ***
+(0.054)</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.553 ***
+(0.055)</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.563 ***
+(0.053)</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.603 ***
+(0.055)</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.697 ***
+(0.064)</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.675 ***
+(0.065)</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.801 ***
+(0.076)</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.829 ***
+(0.086)</v>
+      </c>
+      <c r="K51" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.824 ***
+(0.086)</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="6"/>
+        <v>0.516 ***
+(0.109)</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="7"/>
+        <v>0.52 ***
+(0.12)</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="8"/>
+        <v>0.375 ***
+(0.127)</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="0"/>
+        <v>0.446 ***
+(0.12)</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="1"/>
+        <v>0.638 ***
+(0.113)</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="2"/>
+        <v>0.425 ***
+(0.142)</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="3"/>
+        <v>0.541 ***
+(0.156)</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.763 ***
+(0.141)</v>
+      </c>
+      <c r="K52" t="str">
+        <f t="shared" si="5"/>
+        <v>0.342 
+(0.21)</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.462 ***
+(0.043)</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.461 ***
+(0.043)</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.483 ***
+(0.043)</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.481 ***
+(0.043)</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.541 ***
+(0.05)</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.558 ***
+(0.055)</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.611 ***
+(0.06)</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.626 ***
+(0.067)</v>
+      </c>
+      <c r="K53" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.626 ***
+(0.07)</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="6"/>
+        <v>0.627 ***
+(0.066)</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="7"/>
+        <v>0.672 ***
+(0.066)</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="8"/>
+        <v>0.603 ***
+(0.069)</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="0"/>
+        <v>0.638 ***
+(0.066)</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>0.771 ***
+(0.072)</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="2"/>
+        <v>0.835 ***
+(0.077)</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="3"/>
+        <v>0.794 ***
+(0.09)</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="4"/>
+        <v>0.831 ***
+(0.093)</v>
+      </c>
+      <c r="K54" t="str">
+        <f t="shared" si="5"/>
+        <v>0.844 ***
+(0.1)</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.139 ***
+(0.04)</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.124 ***
+(0.041)</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.138 ***
+(0.039)</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.149 ***
+(0.041)</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.204 ***
+(0.046)</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.21 ***
+(0.049)</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.275 ***
+(0.058)</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.267 ***
+(0.064)</v>
+      </c>
+      <c r="K55" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.22 ***
+(0.065)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.477 ***
+(0.07)</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.463 ***
+(0.077)</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="8"/>
+        <v>-0.322 ***
+(0.094)</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.449 ***
+(0.077)</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="1"/>
+        <v>-0.372 ***
+(0.091)</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="2"/>
+        <v>-0.397 ***
+(0.097)</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="3"/>
+        <v>0.579 ***
+(0.101)</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="4"/>
+        <v>-0.567 ***
+(0.102)</v>
+      </c>
+      <c r="K56" t="str">
+        <f t="shared" si="5"/>
+        <v>-0.421 ***
+(0.136)</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>265</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="6"/>
+        <v>0.189 ***
+(0.04)</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="7"/>
+        <v>0.17 ***
+(0.042)</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="8"/>
+        <v>0.175 ***
+(0.041)</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="0"/>
+        <v>0.196 ***
+(0.042)</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="1"/>
+        <v>0.194 ***
+(0.047)</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="2"/>
+        <v>0.183 ***
+(0.05)</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="3"/>
+        <v>0.18 ***
+(0.059)</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="4"/>
+        <v>0.235 ***
+(0.064)</v>
+      </c>
+      <c r="K57" t="str">
+        <f t="shared" si="5"/>
+        <v>0.237 ***
+(0.067)</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>266</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="6"/>
+        <v>0.737 ***
+(0.058)</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="7"/>
+        <v>0.692 ***
+(0.061)</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" si="8"/>
+        <v>0.7 ***
+(0.062)</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="0"/>
+        <v>0.749 ***
+(0.061)</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="1"/>
+        <v>0.825 ***
+(0.067)</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="2"/>
+        <v>0.85 ***
+(0.074)</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="3"/>
+        <v>-0.969 ***
+(0.08)</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="4"/>
+        <v>0.968 ***
+(0.092)</v>
+      </c>
+      <c r="K58" t="str">
+        <f t="shared" si="5"/>
+        <v>0.877 ***
+(0.095)</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" t="s">
+        <v>267</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="6"/>
+        <v>0.238 ***
+(0.041)</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="7"/>
+        <v>0.233 ***
+(0.042)</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="8"/>
+        <v>0.228 ***
+(0.043)</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="0"/>
+        <v>0.248 ***
+(0.042)</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="1"/>
+        <v>0.259 ***
+(0.049)</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="2"/>
+        <v>0.257 ***
+(0.053)</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="3"/>
+        <v>0.238 ***
+(0.06)</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="4"/>
+        <v>0.238 ***
+(0.066)</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" si="5"/>
+        <v>0.274 ***
+(0.07)</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>268</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="6"/>
+        <v>-0.988 ***
+(0.051)</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="7"/>
+        <v>-0.973 ***
+(0.052)</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="8"/>
+        <v>-1.021 ***
+(0.052)</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="0"/>
+        <v>-1.005 ***
+(0.052)</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="1"/>
+        <v>-1.119 ***
+(0.06)</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="2"/>
+        <v>-1.152 ***
+(0.065)</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="3"/>
+        <v>-1.241 ***
+(0.076)</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="4"/>
+        <v>-1.29 ***
+(0.085)</v>
+      </c>
+      <c r="K60" t="str">
+        <f t="shared" si="5"/>
+        <v>-1.281 ***
+(0.09)</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="6"/>
+        <v>0.92 ***
+(0.039)</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="7"/>
+        <v>0.943 ***
+(0.041)</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="8"/>
+        <v>0.93 ***
+(0.04)</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="0"/>
+        <v>0.956 ***
+(0.041)</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="1"/>
+        <v>0.901 ***
+(0.043)</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="2"/>
+        <v>0.911 ***
+(0.046)</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="3"/>
+        <v>0.861 ***
+(0.047)</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="4"/>
+        <v>0.838 ***
+(0.05)</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="5"/>
+        <v>0.841 ***
+(0.053)</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="6"/>
+        <v>0.943 ***
+(0.04)</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="7"/>
+        <v>0.948 ***
+(0.044)</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" si="8"/>
+        <v>0.944 ***
+(0.041)</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="0"/>
+        <v>0.988 ***
+(0.044)</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="1"/>
+        <v>0.978 ***
+(0.049)</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="2"/>
+        <v>0.98 ***
+(0.052)</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="3"/>
+        <v>0.903 ***
+(0.053)</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="4"/>
+        <v>0.929 ***
+(0.059)</v>
+      </c>
+      <c r="K62" t="str">
+        <f t="shared" si="5"/>
+        <v>0.902 ***
+(0.06)</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>269</v>
+      </c>
+      <c r="C63">
+        <f>ROUND(C27,3)</f>
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="D63">
+        <f>ROUND(F27,3)</f>
+        <v>0.45</v>
+      </c>
+      <c r="E63">
+        <f>ROUND(I27,3)</f>
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="F63">
+        <f>ROUND(L27,3)</f>
+        <v>0.45</v>
+      </c>
+      <c r="G63">
+        <f>ROUND(O27,3)</f>
+        <v>0.443</v>
+      </c>
+      <c r="H63">
+        <f>ROUND(R27,3)</f>
+        <v>0.434</v>
+      </c>
+      <c r="I63">
+        <f>ROUND(U27,3)</f>
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="J63">
+        <f>ROUND(X27,3)</f>
+        <v>0.42</v>
+      </c>
+      <c r="K63">
+        <f>ROUND(AA27,3)</f>
+        <v>0.42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57ed4d19-7dfa-4218-b0c9-321a76363151">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f52a8275-2cbd-4186-978c-53e036657375" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027EAE559E09D4A429EBD0F39DC21BBA6" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1af2fb9fc54a5c91fb7e1af47b87503a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57ed4d19-7dfa-4218-b0c9-321a76363151" xmlns:ns3="f52a8275-2cbd-4186-978c-53e036657375" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1af883276bc8df500be0fc59e8fb9344" ns2:_="" ns3:_="">
     <xsd:import namespace="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
@@ -25602,27 +29484,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1E85CAA-214C-4A93-81C6-DC9EF0A0CEA5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
+    <ds:schemaRef ds:uri="f52a8275-2cbd-4186-978c-53e036657375"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57ed4d19-7dfa-4218-b0c9-321a76363151">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f52a8275-2cbd-4186-978c-53e036657375" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3AF64D9-4533-4B94-B017-1DE81746EA29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80EA8933-6F5C-4438-8751-1038EFECB697}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25641,25 +29522,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3AF64D9-4533-4B94-B017-1DE81746EA29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1E85CAA-214C-4A93-81C6-DC9EF0A0CEA5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
-    <ds:schemaRef ds:uri="f52a8275-2cbd-4186-978c-53e036657375"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{ae525757-89ba-4d30-a2f7-49796ef8c604}" enabled="0" method="" siteId="{ae525757-89ba-4d30-a2f7-49796ef8c604}" removed="1"/>
